--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,6 +778,1235 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129189146</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485896</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6845913</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129188513</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485904</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6845921</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129188956</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485927</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6845919</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129187123</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>485992</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6845639</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129186962</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80176</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>485990</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6845637</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129189354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>485931</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6845961</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129185740</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>485703</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6845675</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129187285</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>485968</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6845654</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129188261</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>485897</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6845909</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129188748</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>485911</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6845919</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129190008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57827</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>485832</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6845801</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129188919</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>485919</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6845922</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>57827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>57827</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R13" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1280,60 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B8" t="n">
-        <v>56913</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R8" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,45 +1377,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>56913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R9" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B12" t="n">
-        <v>57827</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R12" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>57827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R13" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>129185740</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>129189354</v>
       </c>
       <c r="B9" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129187285</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>57829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>57827</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R13" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,45 +1280,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>56915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R8" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,60 +1392,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>56915</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R9" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B12" t="n">
-        <v>57829</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R12" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>57829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R13" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129187285</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>57829</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R13" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1280,60 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B8" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R8" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,45 +1377,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R9" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,45 +1280,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R8" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,60 +1392,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R9" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129187285</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R12" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R13" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,60 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B8" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R8" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,45 +1377,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R9" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1492,7 +1492,7 @@
         <v>129187285</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R13" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,45 +1280,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R8" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,60 +1392,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R9" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,60 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B8" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R8" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,45 +1377,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R9" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R12" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R13" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R13" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,45 +1280,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R8" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,60 +1392,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R9" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1081,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129187123</v>
+        <v>129186962</v>
       </c>
       <c r="B6" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485992</v>
+        <v>485990</v>
       </c>
       <c r="R6" t="n">
-        <v>6845639</v>
+        <v>6845637</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1152,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129186962</v>
+        <v>129187123</v>
       </c>
       <c r="B7" t="n">
-        <v>80185</v>
+        <v>80184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1213,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485990</v>
+        <v>485992</v>
       </c>
       <c r="R7" t="n">
-        <v>6845637</v>
+        <v>6845639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1254,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1081,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129186962</v>
+        <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80185</v>
+        <v>80184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485990</v>
+        <v>485992</v>
       </c>
       <c r="R6" t="n">
-        <v>6845637</v>
+        <v>6845639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129187123</v>
+        <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1189,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485992</v>
+        <v>485990</v>
       </c>
       <c r="R7" t="n">
-        <v>6845639</v>
+        <v>6845637</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R12" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R13" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129188748</v>
+        <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485911</v>
+        <v>485832</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845801</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,42 +1798,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129190008</v>
+        <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485832</v>
+        <v>485911</v>
       </c>
       <c r="R13" t="n">
-        <v>6845801</v>
+        <v>6845919</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129189146</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129188513</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>129188956</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,45 +1280,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129185740</v>
+        <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>56920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485703</v>
+        <v>485931</v>
       </c>
       <c r="R8" t="n">
-        <v>6845675</v>
+        <v>6845961</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,60 +1392,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129189354</v>
+        <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>57890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485931</v>
+        <v>485703</v>
       </c>
       <c r="R9" t="n">
-        <v>6845961</v>
+        <v>6845675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1492,7 +1492,7 @@
         <v>129187285</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129190008</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>129000428</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129189146</v>
+        <v>129186029</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485896</v>
+        <v>485815</v>
       </c>
       <c r="R3" t="n">
-        <v>6845913</v>
+        <v>6845528</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129188513</v>
+        <v>129186072</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485904</v>
+        <v>485802</v>
       </c>
       <c r="R4" t="n">
-        <v>6845921</v>
+        <v>6845542</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129188956</v>
+        <v>129187285</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485927</v>
+        <v>485968</v>
       </c>
       <c r="R5" t="n">
-        <v>6845919</v>
+        <v>6845654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1075,7 @@
         <v>129187123</v>
       </c>
       <c r="B6" t="n">
-        <v>80210</v>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1172,7 @@
         <v>129186962</v>
       </c>
       <c r="B7" t="n">
-        <v>80211</v>
+        <v>80468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1274,7 @@
         <v>129189354</v>
       </c>
       <c r="B8" t="n">
-        <v>56920</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1386,7 @@
         <v>129185740</v>
       </c>
       <c r="B9" t="n">
-        <v>57890</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129187285</v>
+        <v>129190008</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>58057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1500,37 +1491,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hållbäcken, Hållbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485968</v>
+        <v>485832</v>
       </c>
       <c r="R10" t="n">
-        <v>6845654</v>
+        <v>6845801</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129188261</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,42 +1692,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129190008</v>
+        <v>129188513</v>
       </c>
       <c r="B12" t="n">
-        <v>57834</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485832</v>
+        <v>485904</v>
       </c>
       <c r="R12" t="n">
-        <v>6845801</v>
+        <v>6845921</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>129188748</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129188919</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,6 +2007,209 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129188956</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>485927</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6845919</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129189112</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hållbäcken, Hållbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>485896</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6845913</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129186029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129186072</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129187285</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129187123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129186962</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129189354</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129185740</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129190008</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129188261</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129188513</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129188748</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129188919</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129188956</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,8 +2285,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129189112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>